--- a/docs/taxonomy/주제_별칭사전_최종본_v1.xlsx
+++ b/docs/taxonomy/주제_별칭사전_최종본_v1.xlsx
@@ -2731,7 +2731,7 @@
         <v>감정, 기분, 기쁨, 슬픔, 무서움, 두려움, 행복, 속상</v>
       </c>
       <c r="I2" t="str">
-        <v>감정, 기분이, 슬퍼, 슬픔, 무서워, 두려움, 속상</v>
+        <v>감정, 기분이, 슬퍼, 무서워, 속상</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -2871,13 +2871,13 @@
         <v>사랑, 사랑해, 애착, 안아줘, 포옹, 뽀뽀, 품</v>
       </c>
       <c r="I6" t="str">
-        <v>사랑해, 안아 줘, 안아줘, 꼭 안, 포옹, 뽀뽀, 애착</v>
+        <v>사랑, 사랑해, 안아 줘, 안아줘, 꼭 안, 포옹, 뽀뽀, 애착</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>'사랑'만으로는 너무 흔해서 소개 매칭에서 제외</v>
+        <v>2026.10.28 운영자: 단어 중심으로 '사랑' 자체를 매칭 (처음엔 너무 흔해서 뺐으나 운영자 결정으로 포함)</v>
       </c>
     </row>
     <row r="7">
@@ -3606,13 +3606,13 @@
         <v>할머니, 할아버지, 조부모, 외할머니, 친척, 이모, 고모, 삼촌, 사촌</v>
       </c>
       <c r="I27" t="str">
-        <v>할머니, 할아버지, 이모, 고모, 삼촌, 사촌, 외갓집, 친척</v>
+        <v>외갓집, 할머니 댁, 할머니댁, 할아버지 댁, 할머니 집, 할아버지 집, 할머니와, 할아버지와, 할머니를 만나, 할아버지를 만나</v>
       </c>
       <c r="J27" t="str">
         <v/>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>2026.10.28 운영자: 소개 매칭은 '○○ 댁/외갓집'처럼 찾아가는 이야기만. 이름(할머니·이모)만으로는 안 붙임 — 단순 등장이 아니라 함께하는 이야기여야 조부모·친척(엄마·아빠·친구처럼 대부분 비움)</v>
       </c>
     </row>
     <row r="28">
@@ -4201,13 +4201,13 @@
         <v>계절, 날씨, 사계절</v>
       </c>
       <c r="I44" t="str">
-        <v>계절, 사계절, 날씨</v>
+        <v>계절, 날씨, 사계절&gt;nature-season-spring+nature-season-summer+nature-season-autumn+nature-season-winter</v>
       </c>
       <c r="J44" t="str">
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>세부 있음</v>
+        <v>세부 있음. 2026.10.28 운영자: 소개에 '사계절'이 있으면 봄·여름·가을·겨울 4개를 한 칩으로 추천('매칭어&gt;세부+세부' 형식)</v>
       </c>
     </row>
     <row r="45">
@@ -4376,13 +4376,13 @@
         <v>비, 비 오는 날, 비오는날, 장마, 우산, 빗방울, 눈, 눈 오는 날, 함박눈, 눈송이, 바람, 태풍, 무지개, 천둥</v>
       </c>
       <c r="I49" t="str">
-        <v>비가 오, 비 오는, 비오는, 빗방울, 장마, 우산, 눈이 내, 눈 오는, 함박눈, 눈송이, 바람이 불, 태풍, 무지개, 천둥, 번개, 소나기</v>
+        <v>^비 오는, ^비오는, ^눈 오는, ^눈오는, 비가 오, 빗방울, 장마, 우산, 눈이 내, 함박눈, 눈송이, 바람이 불, 태풍, 무지개, 천둥, 번개, 소나기</v>
       </c>
       <c r="J49" t="str">
         <v/>
       </c>
       <c r="K49" t="str">
-        <v/>
+        <v>2026.10.28 운영자: '비 오는 날'처럼 배경만 나오는 말은 소개 매칭에서 뺌(『구름빵』). 단 제목에 있으면 주제라서 '^'(제목에서만 매칭)로 둠 — 『눈 오는 날』. 검색 별칭에는 그대로</v>
       </c>
     </row>
     <row r="50">
@@ -4796,13 +4796,13 @@
         <v>환경, 지구, 쓰레기, 재활용, 분리수거, 플라스틱, 기후, 오염, 자연보호</v>
       </c>
       <c r="I61" t="str">
-        <v>환경, 지구를, 쓰레기, 재활용, 분리수거, 플라스틱, 기후, 오염</v>
+        <v>환경 보호, 환경을 지, 환경오염, 지구를 지, 지구가 아, 쓰레기, 재활용, 분리수거, 플라스틱, 기후 위기, 기후 변화, 오염</v>
       </c>
       <c r="J61" t="str">
         <v/>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>2026.10.28: '환경' 단독은 '그런 환경에'처럼 일반 뜻으로도 쓰여 뺌(『이사 가는 날』)</v>
       </c>
     </row>
     <row r="62">
@@ -5391,13 +5391,13 @@
         <v>음식, 먹거리, 요리, 간식, 초밥, 김밥, 국수, 만두, 떡, 요리하기, 요리사, 요리 놀이</v>
       </c>
       <c r="I78" t="str">
-        <v>음식, 요리, 김밥, 초밥, 국수, 만두, 요리사, 요리 놀이</v>
+        <v>요리, 김밥, 초밥, 국수, 만두, 요리사, 요리 놀이</v>
       </c>
       <c r="J78" t="str">
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>세부 있음</v>
+        <v>2026.10.28: '음식' 단독은 '정성 가득한 음식'처럼 소재가 아닌 곳에도 나와 소개 매칭에서 뺌(『할머니 집에 가는 길』). 세부 있음</v>
       </c>
     </row>
     <row r="79">
@@ -6091,7 +6091,7 @@
         <v>마법, 요술, 신기한, 마술, 마법사, 다른 세계, 이상한 나라, 상상 나라, 비밀의 문, 작아지, 커지</v>
       </c>
       <c r="I98" t="str">
-        <v>마법, 요술, 마술사, 마법사, 신기한 일, 이상한 나라, 다른 세계, 비밀의 문, 작아져, 커져, 작아지, 커지</v>
+        <v>마법, 요술, 마법사, 신기한 일, 이상한 나라, 다른 세계, 비밀의 문, 작아져, 커져, 작아지, 커지</v>
       </c>
       <c r="J98" t="str">
         <v/>
